--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="10" activeTab="20"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="12" activeTab="22"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -33,6 +33,8 @@
     <sheet name="20260809" sheetId="93" r:id="rId19"/>
     <sheet name="20260816" sheetId="94" r:id="rId20"/>
     <sheet name="20260823" sheetId="95" r:id="rId21"/>
+    <sheet name="20260830" sheetId="96" r:id="rId22"/>
+    <sheet name="20260906" sheetId="97" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="485">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -637,9 +639,6 @@
   </si>
   <si>
     <t>Hǎo zhǔ yì. Wǒ huì dài shàng wǒ de tóu kuī hé shuǐ hú.</t>
-  </si>
-  <si>
-    <t>人</t>
   </si>
   <si>
     <t>A: 我也是。我们下午三点在公园入口见吧。</t>
@@ -1576,6 +1575,96 @@
   <si>
     <t>Guānjiàn kàn yòng de rén zěnme yòng.</t>
   </si>
+  <si>
+    <t>A：小李，你骑这么快，脸色怎么这么白？</t>
+  </si>
+  <si>
+    <t>A：Xiǎo Lǐ, nǐ qí zhè me kuài, liǎn sè zěn me zhè me bái?</t>
+  </si>
+  <si>
+    <t>A: Xiao Li, you’re riding so fast, but why is your face so pale?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B：我有点头晕，手也开始发抖了。 </t>
+  </si>
+  <si>
+    <t>B：Wǒ yǒu diǎn tóu yūn, shǒu yě kāi shǐ fā dǒu le.</t>
+  </si>
+  <si>
+    <t>B: I feel a little dizzy, and my hands are starting to shake.</t>
+  </si>
+  <si>
+    <t>A：是不是低血糖了？你早上没吃早饭吗？</t>
+  </si>
+  <si>
+    <t>A：Shì bú shì dī xuè táng le? Nǐ zǎo shàng méi chī zǎo fàn ma?</t>
+  </si>
+  <si>
+    <t>A: Is it low blood sugar? Didn’t you have breakfast this morning?</t>
+  </si>
+  <si>
+    <t>B：出门太急，我只喝了半杯温水。</t>
+  </si>
+  <si>
+    <t>B：Chū mén tài jí, wǒ zhǐ hē le bàn bēi wēn shuǐ.</t>
+  </si>
+  <si>
+    <t>B: I was in such a hurry going out that I only drank half a cup of warm water.</t>
+  </si>
+  <si>
+    <t>A：快停下车子，我包里有橘子糖。</t>
+  </si>
+  <si>
+    <t>A：Kuài tíng xià chē zi, wǒ bāo lǐ yǒu jú zi táng.</t>
+  </si>
+  <si>
+    <t>A: Stop the bike quickly. I have orange candies in my bag.</t>
+  </si>
+  <si>
+    <t>B：好，我扶着树慢慢下来，腿有点软。</t>
+  </si>
+  <si>
+    <t>B：Hǎo, wǒ fú zhe shù màn màn xià lái, tuǐ yǒu diǎn ruǎn.</t>
+  </si>
+  <si>
+    <t>B: Okay, I’m holding the tree to get off slowly — my legs feel a little weak.</t>
+  </si>
+  <si>
+    <t>A：先含一颗糖，别着急大口喝水。</t>
+  </si>
+  <si>
+    <t>A：Xiān hán yī kē táng, bié zháo jí dà kǒu hē shuǐ.</t>
+  </si>
+  <si>
+    <t>A: Put a candy in your mouth first. Don’t rush to drink water in big gulps.</t>
+  </si>
+  <si>
+    <t>B：谢谢你，刚才眼前都有点发黑了。</t>
+  </si>
+  <si>
+    <t>B：Xiè xie nǐ, gāng cái yǎn qián dōu yǒu diǎn fā hēi le.</t>
+  </si>
+  <si>
+    <t>B: Thank you. My vision almost went dark just now.</t>
+  </si>
+  <si>
+    <t>A：下次骑车前，一定要带点小糖果。</t>
+  </si>
+  <si>
+    <t>A：Xià cì qí chē qián, yī dìng yào dài diǎn xiǎo táng guǒ.</t>
+  </si>
+  <si>
+    <t>A: Next time before you go cycling, you must bring some small candies with you.</t>
+  </si>
+  <si>
+    <t>B：我记住了，运动前可不能空着肚子。</t>
+  </si>
+  <si>
+    <t>B：Wǒ jì zhù le, yùn dòng qián kě bù néng kōng zhe dù zi.</t>
+  </si>
+  <si>
+    <t>B: I’ve got it. You must never do exercise on an empty stomach.</t>
+  </si>
 </sst>
 </file>
 
@@ -1587,7 +1676,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1598,6 +1687,12 @@
       <sz val="11"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="等线 Light"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2104,19 +2199,16 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2125,119 +2217,122 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2245,9 +2340,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2876,7 +2972,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="2"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -2905,7 +3001,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="7"/>
+      <c r="C11" s="8"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -2924,7 +3020,7 @@
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="3"/>
       <c r="V15" s="1" t="s">
         <v>14</v>
       </c>
@@ -2933,16 +3029,16 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V16" s="3"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="3"/>
+      <c r="C17" s="4"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="2"/>
+      <c r="C18" s="3"/>
       <c r="V18" s="1" t="s">
         <v>17</v>
       </c>
@@ -2959,19 +3055,19 @@
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="5"/>
       <c r="V21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="V22" s="3"/>
+      <c r="V22" s="4"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="2"/>
+      <c r="B23" s="3"/>
     </row>
     <row r="24" spans="2:26">
       <c r="B24" s="1" t="s">
@@ -3013,7 +3109,7 @@
       </c>
     </row>
     <row r="32" spans="2:26">
-      <c r="C32" s="8"/>
+      <c r="C32" s="9"/>
     </row>
     <row r="33" spans="2:29">
       <c r="B33" s="1" t="s">
@@ -3022,7 +3118,7 @@
       <c r="V33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC33" s="3"/>
+      <c r="AC33" s="4"/>
     </row>
     <row r="34" spans="2:29">
       <c r="C34" s="1" t="s">
@@ -3054,111 +3150,111 @@
     </row>
     <row r="3" spans="2:22">
       <c r="B3" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="V3" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="4" spans="2:22">
       <c r="C4" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" ht="15" spans="2:22">
       <c r="B6" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="S6" s="7"/>
+      <c r="V6" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="S6" s="6"/>
-      <c r="V6" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="7" spans="2:22">
       <c r="C7" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="2:22">
       <c r="B9" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="V9" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="10" spans="2:22">
       <c r="C10" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" spans="2:22">
       <c r="V13" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="2:22">
       <c r="C14" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15" spans="2:22">
       <c r="B15" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="V15" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="16" spans="2:22">
       <c r="C16" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" spans="2:22">
       <c r="B18" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="V18" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="V18" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="19" spans="2:22">
       <c r="C19" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" spans="2:22">
       <c r="B21" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" spans="2:22">
       <c r="V22" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" spans="2:22">
       <c r="C23" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="2:22">
       <c r="B25" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="V25" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="V25" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="26" spans="2:22">
       <c r="C26" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -3186,107 +3282,107 @@
     </row>
     <row r="3" spans="2:24">
       <c r="B3" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="X3" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="4" spans="2:24">
       <c r="C4" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" ht="15" spans="2:24">
       <c r="B6" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="S6" s="7"/>
+      <c r="X6" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="S6" s="6"/>
-      <c r="X6" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="7" spans="2:24">
       <c r="C7" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="2:24">
       <c r="B9" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="X9" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="10" spans="2:24">
       <c r="C10" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="2:24">
       <c r="B12" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="X12" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="X12" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="13" spans="2:24">
       <c r="C13" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="15" spans="2:24">
       <c r="B15" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="X15" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="X15" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="16" spans="2:24">
       <c r="C16" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="2:24">
       <c r="B18" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="X18" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="X18" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="19" spans="2:24">
       <c r="C19" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="21" spans="2:24">
       <c r="B21" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="X21" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="X21" s="1" t="s">
+    </row>
+    <row r="22" spans="2:24">
+      <c r="C22" s="10" t="s">
         <v>278</v>
-      </c>
-    </row>
-    <row r="22" spans="2:24">
-      <c r="C22" s="9" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="24" spans="2:24">
       <c r="B24" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="X24" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="X24" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="25" spans="2:24">
       <c r="C25" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -3314,123 +3410,123 @@
     </row>
     <row r="2" spans="2:22">
       <c r="C2" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="3" spans="2:22">
       <c r="C3" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="2:22">
       <c r="C5" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="V5" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="6" ht="15" spans="2:22">
       <c r="C6" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="S6" s="6"/>
+        <v>287</v>
+      </c>
+      <c r="S6" s="7"/>
     </row>
     <row r="8" spans="2:22">
       <c r="C8" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="V8" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="9" spans="2:22">
       <c r="C9" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="2:22">
       <c r="C11" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="V11" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="V11" s="1" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="12" spans="2:22">
       <c r="C12" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" spans="2:22">
       <c r="C14" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="V14" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="V14" s="1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="15" spans="2:22">
       <c r="C15" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="17" spans="3:22">
       <c r="C17" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="V17" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="V17" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="18" spans="3:22">
       <c r="C18" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20" spans="3:22">
       <c r="C20" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="V20" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="V20" s="1" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="21" spans="3:22">
       <c r="C21" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="22" spans="3:22">
-      <c r="C22" s="9"/>
+      <c r="C22" s="10"/>
     </row>
     <row r="23" spans="3:22">
       <c r="C23" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="V23" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="V23" s="1" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="24" spans="3:22">
       <c r="C24" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" spans="3:22">
       <c r="C26" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="V26" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="V26" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="27" spans="3:22">
       <c r="C27" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3458,125 +3554,125 @@
     </row>
     <row r="3" spans="2:24">
       <c r="B3" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="X3" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="4" spans="2:24">
       <c r="C4" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="2:24">
       <c r="C5" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" ht="15" spans="2:24">
       <c r="B6" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="S6" s="7"/>
+      <c r="X6" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="S6" s="6"/>
-      <c r="X6" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="7" spans="2:24">
       <c r="C7" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" spans="2:24">
       <c r="B9" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="X9" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="10" spans="2:24">
       <c r="C10" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="12" spans="2:24">
       <c r="B12" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="X12" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="X12" s="1" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="13" spans="2:24">
       <c r="C13" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" spans="2:24">
       <c r="B15" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="X15" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="X15" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="16" spans="2:24">
       <c r="C16" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18" spans="2:24">
       <c r="B18" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="X18" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="X18" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="19" spans="2:24">
       <c r="C19" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="21" spans="2:24">
       <c r="B21" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="X21" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="X21" s="1" t="s">
+    </row>
+    <row r="22" spans="2:24">
+      <c r="C22" s="10" t="s">
         <v>330</v>
-      </c>
-    </row>
-    <row r="22" spans="2:24">
-      <c r="C22" s="9" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="24" spans="2:24">
       <c r="B24" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="X24" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="X24" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="25" spans="2:24">
       <c r="C25" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="27" spans="2:24">
       <c r="B27" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="X27" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="X27" s="1" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="28" spans="2:24">
       <c r="C28" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -3604,113 +3700,113 @@
     </row>
     <row r="3" spans="2:22">
       <c r="B3" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="V3" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="4" spans="2:22">
       <c r="C4" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" ht="15" spans="2:22">
       <c r="B6" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="S6" s="7"/>
+      <c r="V6" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="S6" s="6"/>
-      <c r="V6" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="7" spans="2:22">
       <c r="C7" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" spans="2:22">
       <c r="B9" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="V9" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="10" spans="2:22">
       <c r="C10" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="V12" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="V12" s="1" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="13" spans="2:22">
       <c r="C13" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" spans="2:22">
       <c r="B15" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="V15" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="16" spans="2:22">
       <c r="C16" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="18" spans="2:22">
       <c r="B18" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="V18" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="V18" s="1" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="19" spans="2:22">
       <c r="C19" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" spans="2:22">
       <c r="B21" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C21" s="10"/>
+      <c r="V21" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="C21" s="9"/>
-      <c r="V21" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="22" spans="2:22">
       <c r="C22" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="24" spans="2:22">
       <c r="B24" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="V24" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="V24" s="1" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="25" spans="2:22">
       <c r="C25" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="27" spans="2:22">
       <c r="L27" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -3792,7 +3888,7 @@
       <c r="B11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
       <c r="P11" s="1" t="s">
         <v>68</v>
       </c>
@@ -3801,36 +3897,36 @@
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="3"/>
+      <c r="V12" s="4"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="3"/>
       <c r="P13" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="14" spans="2:22">
       <c r="C14" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" spans="2:22">
       <c r="B15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="5"/>
       <c r="P15" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="3"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="17" spans="2:29">
       <c r="B17" s="1" t="s">
@@ -3878,7 +3974,7 @@
       <c r="P23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AC23" s="3"/>
+      <c r="AC23" s="4"/>
     </row>
     <row r="24" spans="2:29">
       <c r="C24" s="1" t="s">
@@ -3936,140 +4032,140 @@
     </row>
     <row r="3" spans="2:22">
       <c r="B3" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="4" spans="2:22">
       <c r="C4" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="2:22">
       <c r="B5" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="S5" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="6" spans="2:22">
       <c r="C6" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="2:22">
       <c r="B7" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="S7" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="8" spans="2:22">
       <c r="C8" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9" spans="2:22">
       <c r="B9" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="S9" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="S9" s="1" t="s">
+      <c r="V9" s="4"/>
+    </row>
+    <row r="10" spans="2:22">
+      <c r="C10" s="3" t="s">
         <v>374</v>
-      </c>
-      <c r="V9" s="3"/>
-    </row>
-    <row r="10" spans="2:22">
-      <c r="C10" s="2" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="11" spans="2:22">
       <c r="B11" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="S11" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="S11" s="1" t="s">
+    </row>
+    <row r="12" ht="14" customHeight="1" spans="2:22">
+      <c r="C12" s="6" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="12" ht="14" customHeight="1" spans="2:22">
-      <c r="C12" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="V12" s="3"/>
+      <c r="V12" s="4"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="S13" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="14" spans="2:22">
       <c r="C14" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="2:22">
       <c r="K15" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="16" spans="2:22">
       <c r="B16" t="s">
+        <v>382</v>
+      </c>
+      <c r="S16" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="17" spans="2:19">
       <c r="C17" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="18" spans="2:19">
       <c r="B18" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="S18" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="19" spans="2:19">
       <c r="C19" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="20" spans="2:19">
       <c r="B20" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="S20" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="21" spans="2:19">
       <c r="C21" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="22" spans="2:19">
       <c r="B22" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="S22" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="23" spans="2:19">
       <c r="C23" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -4097,145 +4193,145 @@
     </row>
     <row r="2" spans="2:22">
       <c r="C2" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3" spans="2:22">
       <c r="B3" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="V3" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="4" spans="2:22">
       <c r="C4" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="V6" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="7" spans="2:22">
       <c r="B7" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="2:22">
-      <c r="V8" s="3"/>
+      <c r="V8" s="4"/>
     </row>
     <row r="9" spans="2:22">
       <c r="B9" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="V9" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="V9" s="1" t="s">
+    </row>
+    <row r="10" spans="2:22">
+      <c r="C10" s="5" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="10" spans="2:22">
-      <c r="C10" s="4" t="s">
-        <v>404</v>
-      </c>
-    </row>
     <row r="11" ht="14" customHeight="1" spans="2:22">
-      <c r="C11" s="5"/>
-      <c r="V11" s="3"/>
+      <c r="C11" s="6"/>
+      <c r="V11" s="4"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="V12" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="V12" s="1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="13" spans="2:22">
       <c r="C13" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="15" spans="2:22">
       <c r="B15" t="s">
+        <v>407</v>
+      </c>
+      <c r="V15" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="16" spans="2:22">
       <c r="C16" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="18" spans="2:22">
       <c r="B18" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="V18" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="V18" s="1" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="19" spans="2:22">
       <c r="C19" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="21" spans="2:22">
       <c r="B21" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="V21" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="V21" s="1" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="22" spans="2:22">
       <c r="C22" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="24" spans="2:22">
       <c r="B24" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="V24" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="V24" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="25" spans="2:22">
       <c r="C25" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="27" spans="2:22">
       <c r="B27" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="V27" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="V27" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="28" spans="2:22">
       <c r="C28" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="30" spans="2:22">
       <c r="B30" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="V30" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="V30" s="1" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="31" spans="2:22">
       <c r="C31" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -4275,7 +4371,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="2"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -4304,7 +4400,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="7"/>
+      <c r="C11" s="8"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -4323,7 +4419,7 @@
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="3"/>
       <c r="V15" s="1" t="s">
         <v>14</v>
       </c>
@@ -4332,16 +4428,16 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V16" s="3"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="3"/>
+      <c r="C17" s="4"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="2"/>
+      <c r="C18" s="3"/>
       <c r="V18" s="1" t="s">
         <v>17</v>
       </c>
@@ -4358,19 +4454,19 @@
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="5"/>
       <c r="V21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="V22" s="3"/>
+      <c r="V22" s="4"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="2"/>
+      <c r="B23" s="3"/>
     </row>
     <row r="24" spans="2:26">
       <c r="B24" s="1" t="s">
@@ -4412,7 +4508,7 @@
       </c>
     </row>
     <row r="32" spans="2:26">
-      <c r="C32" s="8"/>
+      <c r="C32" s="9"/>
     </row>
     <row r="33" spans="2:29">
       <c r="B33" s="1" t="s">
@@ -4421,7 +4517,7 @@
       <c r="V33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC33" s="3"/>
+      <c r="AC33" s="4"/>
     </row>
     <row r="34" spans="2:29">
       <c r="C34" s="1" t="s">
@@ -4453,111 +4549,111 @@
     </row>
     <row r="3" spans="2:22">
       <c r="B3" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="V3" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="4" spans="2:22">
       <c r="C4" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" ht="15" spans="2:22">
       <c r="B6" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="S6" s="7"/>
+      <c r="V6" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="S6" s="6"/>
-      <c r="V6" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="7" spans="2:22">
       <c r="C7" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="2:22">
       <c r="B9" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="V9" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="10" spans="2:22">
       <c r="C10" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" spans="2:22">
       <c r="V13" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="2:22">
       <c r="C14" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15" spans="2:22">
       <c r="B15" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="V15" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="16" spans="2:22">
       <c r="C16" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" spans="2:22">
       <c r="B18" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="V18" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="V18" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="19" spans="2:22">
       <c r="C19" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" spans="2:22">
       <c r="B21" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" spans="2:22">
       <c r="V22" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" spans="2:22">
       <c r="C23" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="24" spans="2:22">
       <c r="B24" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="V24" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="V24" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="25" spans="2:22">
       <c r="C25" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -4597,7 +4693,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="2"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -4626,7 +4722,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="7"/>
+      <c r="C11" s="8"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -4645,7 +4741,7 @@
       <c r="B15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="3"/>
       <c r="U15" s="1" t="s">
         <v>47</v>
       </c>
@@ -4654,16 +4750,16 @@
       <c r="C16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="V16" s="3"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="3"/>
+      <c r="C17" s="4"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="2"/>
+      <c r="C18" s="3"/>
       <c r="U18" s="1" t="s">
         <v>50</v>
       </c>
@@ -4680,28 +4776,28 @@
       <c r="B21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="5"/>
       <c r="U21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="V22" s="3"/>
+      <c r="V22" s="4"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="2"/>
+      <c r="B23" s="3"/>
     </row>
     <row r="30" spans="2:26">
       <c r="B30"/>
     </row>
     <row r="32" spans="2:26">
-      <c r="C32" s="8"/>
+      <c r="C32" s="9"/>
     </row>
     <row r="33" spans="29:29">
-      <c r="AC33" s="3"/>
+      <c r="AC33" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4728,133 +4824,133 @@
     </row>
     <row r="3" spans="2:19">
       <c r="B3" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="4" spans="2:19">
       <c r="C4" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" ht="15" spans="2:19">
       <c r="B6" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="R6" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="R6" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="S6" s="6"/>
+      <c r="S6" s="7"/>
     </row>
     <row r="7" spans="2:19">
       <c r="C7" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9" spans="2:19">
       <c r="B9" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="R9" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="10" spans="2:19">
       <c r="C10" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" spans="2:19">
       <c r="B12" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="R12" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="13" spans="2:19">
       <c r="C13" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="15" spans="2:19">
       <c r="B15" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="R15" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="16" spans="2:19">
       <c r="C16" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="18" spans="2:18">
       <c r="B18" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="R18" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="19" spans="2:18">
       <c r="C19" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="21" spans="2:18">
       <c r="B21" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="R21" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="22" spans="2:18">
       <c r="C22" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="24" spans="2:18">
       <c r="B24" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="R24" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="25" spans="2:18">
       <c r="C25" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="27" spans="2:18">
       <c r="B27" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="R27" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="28" spans="2:18">
       <c r="C28" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="30" spans="2:18">
       <c r="B30" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="R30" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="31" spans="2:18">
       <c r="C31" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -4918,13 +5014,13 @@
       <c r="B11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="2:23">
-      <c r="V12" s="3"/>
+      <c r="V12" s="4"/>
     </row>
     <row r="13" spans="2:23">
-      <c r="C13" s="2"/>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="2:23">
       <c r="B14" s="1" t="s">
@@ -4938,11 +5034,11 @@
       <c r="B15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="5"/>
     </row>
     <row r="16" spans="2:23">
-      <c r="C16" s="5"/>
-      <c r="V16" s="3"/>
+      <c r="C16" s="6"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -4971,7 +5067,301 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="3"/>
+      <c r="AC23" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:S28"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:19">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:19">
+      <c r="B3" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19">
+      <c r="C4" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" ht="15.6" spans="2:19">
+      <c r="B6" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19">
+      <c r="C7" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19">
+      <c r="B9" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19">
+      <c r="C10" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19">
+      <c r="B12" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19">
+      <c r="C13" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19">
+      <c r="B15" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19">
+      <c r="C16" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19">
+      <c r="B18" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19">
+      <c r="C19" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19">
+      <c r="B21" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19">
+      <c r="C22" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19">
+      <c r="B24" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19">
+      <c r="C25" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19">
+      <c r="B27" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19">
+      <c r="C28" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:X31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24">
+      <c r="A3" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
+      <c r="B4" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="6" ht="15.6" spans="1:24">
+      <c r="A6" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="S6" s="2"/>
+    </row>
+    <row r="7" spans="1:24">
+      <c r="B7" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
+      <c r="A9" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="B10" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="A12" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
+      <c r="B13" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
+      <c r="A15" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24">
+      <c r="B16" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24">
+      <c r="A18" s="1" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24">
+      <c r="B19" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24">
+      <c r="A21" s="1" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24">
+      <c r="B22" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24">
+      <c r="A24" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24">
+      <c r="B25" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24">
+      <c r="A27" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24">
+      <c r="B28" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24">
+      <c r="A30" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24">
+      <c r="B31" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="X31" s="1" t="s">
+        <v>484</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -5052,7 +5442,7 @@
       <c r="B11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
       <c r="P11" s="1" t="s">
         <v>68</v>
       </c>
@@ -5061,13 +5451,13 @@
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="3"/>
+      <c r="V12" s="4"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="3"/>
       <c r="P13" s="1" t="s">
         <v>71</v>
       </c>
@@ -5081,16 +5471,16 @@
       <c r="B15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="5"/>
       <c r="P15" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="3"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="17" spans="2:29">
       <c r="B17" s="1" t="s">
@@ -5138,7 +5528,7 @@
       <c r="P23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AC23" s="3"/>
+      <c r="AC23" s="4"/>
     </row>
     <row r="24" spans="2:29">
       <c r="C24" s="1" t="s">
@@ -5232,13 +5622,13 @@
       <c r="B11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="2:23">
-      <c r="V12" s="3"/>
+      <c r="V12" s="4"/>
     </row>
     <row r="13" spans="2:23">
-      <c r="C13" s="2"/>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="2:23">
       <c r="B14" s="1" t="s">
@@ -5252,11 +5642,11 @@
       <c r="B15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="5"/>
     </row>
     <row r="16" spans="2:23">
-      <c r="C16" s="5"/>
-      <c r="V16" s="3"/>
+      <c r="C16" s="6"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -5285,7 +5675,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="3"/>
+      <c r="AC23" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -5350,16 +5740,16 @@
       </c>
     </row>
     <row r="11" spans="2:26">
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="2:26">
       <c r="B12" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="V12" s="3"/>
+      <c r="V12" s="4"/>
     </row>
     <row r="13" spans="2:26">
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>122</v>
       </c>
     </row>
@@ -5372,16 +5762,16 @@
       <c r="B15" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="5"/>
       <c r="Z15" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="16" spans="2:26">
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="V16" s="3"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="17" spans="2:29">
       <c r="Z17" s="1" t="s">
@@ -5420,7 +5810,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="3"/>
+      <c r="AC23" s="4"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">
@@ -5498,7 +5888,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="2"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -5509,7 +5899,7 @@
       </c>
     </row>
     <row r="13" spans="2:22">
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5517,16 +5907,16 @@
       <c r="B15" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="5"/>
       <c r="V15" s="1" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="V16" s="3"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -5555,7 +5945,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="3"/>
+      <c r="AC23" s="4"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">
@@ -5760,61 +6150,56 @@
         <v>194</v>
       </c>
     </row>
-    <row r="12" spans="2:20">
-      <c r="M12" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
     <row r="13" spans="2:20">
       <c r="B13" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="T13" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="14" spans="2:20">
       <c r="C14" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="2:20">
       <c r="B16" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="T16" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="17" spans="2:20">
       <c r="C17" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="2:20">
       <c r="B19" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="T19" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="20" spans="2:20">
       <c r="C20" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" spans="2:20">
       <c r="B22" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="T22" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="23" spans="2:20">
       <c r="C23" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -5842,119 +6227,119 @@
     </row>
     <row r="3" spans="2:19">
       <c r="B3" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="4" spans="2:19">
       <c r="C4" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" ht="15" spans="2:19">
       <c r="B6" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="S6" s="7" t="s">
         <v>211</v>
-      </c>
-      <c r="S6" s="6" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="7" spans="2:19">
       <c r="C7" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="2:19">
       <c r="B9" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="S9" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="10" spans="2:19">
       <c r="C10" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="2:19">
       <c r="B12" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="S12" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="13" spans="2:19">
       <c r="C13" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="2:19">
       <c r="B15" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="S15" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="16" spans="2:19">
       <c r="C16" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="2:19">
       <c r="B18" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="S18" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="19" spans="2:19">
       <c r="C19" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="2:19">
       <c r="B21" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="S21" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="22" spans="2:19">
       <c r="C22" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="2:19">
       <c r="B24" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="S24" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="25" spans="2:19">
       <c r="C25" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="2:19">
       <c r="B27" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="S27" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="28" spans="2:19">
       <c r="C28" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="12" activeTab="22"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="13" activeTab="23"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -35,6 +35,7 @@
     <sheet name="20260823" sheetId="95" r:id="rId21"/>
     <sheet name="20260830" sheetId="96" r:id="rId22"/>
     <sheet name="20260906" sheetId="97" r:id="rId23"/>
+    <sheet name="20260913" sheetId="98" r:id="rId24"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="485">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -1686,6 +1687,17 @@
     <font>
       <sz val="11"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1718,20 +1730,9 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2341,8 +2342,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2972,7 +2973,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="3"/>
+      <c r="C5" s="5"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -3001,7 +3002,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="8"/>
+      <c r="C11" s="9"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -3020,7 +3021,7 @@
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="5"/>
       <c r="V15" s="1" t="s">
         <v>14</v>
       </c>
@@ -3029,16 +3030,16 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="6"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="4"/>
+      <c r="C17" s="6"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="5"/>
       <c r="V18" s="1" t="s">
         <v>17</v>
       </c>
@@ -3055,19 +3056,19 @@
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="5"/>
+      <c r="C21" s="7"/>
       <c r="V21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="V22" s="4"/>
+      <c r="V22" s="6"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="3"/>
+      <c r="B23" s="5"/>
     </row>
     <row r="24" spans="2:26">
       <c r="B24" s="1" t="s">
@@ -3109,7 +3110,7 @@
       </c>
     </row>
     <row r="32" spans="2:26">
-      <c r="C32" s="9"/>
+      <c r="C32" s="10"/>
     </row>
     <row r="33" spans="2:29">
       <c r="B33" s="1" t="s">
@@ -3118,7 +3119,7 @@
       <c r="V33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC33" s="4"/>
+      <c r="AC33" s="6"/>
     </row>
     <row r="34" spans="2:29">
       <c r="C34" s="1" t="s">
@@ -3165,7 +3166,7 @@
       <c r="B6" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="S6" s="7"/>
+      <c r="S6" s="2"/>
       <c r="V6" s="1" t="s">
         <v>238</v>
       </c>
@@ -3297,7 +3298,7 @@
       <c r="B6" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="S6" s="7"/>
+      <c r="S6" s="2"/>
       <c r="X6" s="1" t="s">
         <v>262</v>
       </c>
@@ -3368,7 +3369,7 @@
       </c>
     </row>
     <row r="22" spans="2:24">
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="3" t="s">
         <v>278</v>
       </c>
     </row>
@@ -3433,7 +3434,7 @@
       <c r="C6" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="S6" s="7"/>
+      <c r="S6" s="2"/>
     </row>
     <row r="8" spans="2:22">
       <c r="C8" s="1" t="s">
@@ -3501,7 +3502,7 @@
       </c>
     </row>
     <row r="22" spans="3:22">
-      <c r="C22" s="10"/>
+      <c r="C22" s="3"/>
     </row>
     <row r="23" spans="3:22">
       <c r="C23" s="1" t="s">
@@ -3574,7 +3575,7 @@
       <c r="B6" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="S6" s="7"/>
+      <c r="S6" s="2"/>
       <c r="X6" s="1" t="s">
         <v>314</v>
       </c>
@@ -3645,7 +3646,7 @@
       </c>
     </row>
     <row r="22" spans="2:24">
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="3" t="s">
         <v>330</v>
       </c>
     </row>
@@ -3715,7 +3716,7 @@
       <c r="B6" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="S6" s="7"/>
+      <c r="S6" s="2"/>
       <c r="V6" s="1" t="s">
         <v>341</v>
       </c>
@@ -3781,7 +3782,7 @@
       <c r="B21" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="3"/>
       <c r="V21" s="1" t="s">
         <v>356</v>
       </c>
@@ -3888,7 +3889,7 @@
       <c r="B11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="5"/>
       <c r="P11" s="1" t="s">
         <v>68</v>
       </c>
@@ -3897,13 +3898,13 @@
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="4"/>
+      <c r="V12" s="6"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="5"/>
       <c r="P13" s="1" t="s">
         <v>71</v>
       </c>
@@ -3917,16 +3918,16 @@
       <c r="B15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="7"/>
       <c r="P15" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="6"/>
     </row>
     <row r="17" spans="2:29">
       <c r="B17" s="1" t="s">
@@ -3974,7 +3975,7 @@
       <c r="P23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AC23" s="4"/>
+      <c r="AC23" s="6"/>
     </row>
     <row r="24" spans="2:29">
       <c r="C24" s="1" t="s">
@@ -4076,10 +4077,10 @@
       <c r="S9" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="V9" s="4"/>
+      <c r="V9" s="6"/>
     </row>
     <row r="10" spans="2:22">
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>374</v>
       </c>
     </row>
@@ -4087,16 +4088,16 @@
       <c r="B11" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C11" s="5"/>
+      <c r="C11" s="7"/>
       <c r="S11" s="1" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1" spans="2:22">
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="V12" s="4"/>
+      <c r="V12" s="6"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
@@ -4223,25 +4224,25 @@
       </c>
     </row>
     <row r="8" spans="2:22">
-      <c r="V8" s="4"/>
+      <c r="V8" s="6"/>
     </row>
     <row r="9" spans="2:22">
       <c r="B9" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="5"/>
       <c r="V9" s="1" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="10" spans="2:22">
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="7" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1" spans="2:22">
-      <c r="C11" s="6"/>
-      <c r="V11" s="4"/>
+      <c r="C11" s="8"/>
+      <c r="V11" s="6"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -4371,7 +4372,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="3"/>
+      <c r="C5" s="5"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -4400,7 +4401,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="8"/>
+      <c r="C11" s="9"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -4419,7 +4420,7 @@
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="5"/>
       <c r="V15" s="1" t="s">
         <v>14</v>
       </c>
@@ -4428,16 +4429,16 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="6"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="4"/>
+      <c r="C17" s="6"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="5"/>
       <c r="V18" s="1" t="s">
         <v>17</v>
       </c>
@@ -4454,19 +4455,19 @@
       <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="5"/>
+      <c r="C21" s="7"/>
       <c r="V21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="V22" s="4"/>
+      <c r="V22" s="6"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="3"/>
+      <c r="B23" s="5"/>
     </row>
     <row r="24" spans="2:26">
       <c r="B24" s="1" t="s">
@@ -4508,7 +4509,7 @@
       </c>
     </row>
     <row r="32" spans="2:26">
-      <c r="C32" s="9"/>
+      <c r="C32" s="10"/>
     </row>
     <row r="33" spans="2:29">
       <c r="B33" s="1" t="s">
@@ -4517,7 +4518,7 @@
       <c r="V33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC33" s="4"/>
+      <c r="AC33" s="6"/>
     </row>
     <row r="34" spans="2:29">
       <c r="C34" s="1" t="s">
@@ -4564,7 +4565,7 @@
       <c r="B6" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="S6" s="7"/>
+      <c r="S6" s="2"/>
       <c r="V6" s="1" t="s">
         <v>238</v>
       </c>
@@ -4693,7 +4694,7 @@
       </c>
     </row>
     <row r="5" spans="2:22">
-      <c r="C5" s="3"/>
+      <c r="C5" s="5"/>
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="1" t="s">
@@ -4722,7 +4723,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="8"/>
+      <c r="C11" s="9"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -4741,7 +4742,7 @@
       <c r="B15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="5"/>
       <c r="U15" s="1" t="s">
         <v>47</v>
       </c>
@@ -4750,16 +4751,16 @@
       <c r="C16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="6"/>
     </row>
     <row r="17" spans="2:26">
-      <c r="C17" s="4"/>
+      <c r="C17" s="6"/>
     </row>
     <row r="18" spans="2:26">
       <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="5"/>
       <c r="U18" s="1" t="s">
         <v>50</v>
       </c>
@@ -4776,28 +4777,28 @@
       <c r="B21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="5"/>
+      <c r="C21" s="7"/>
       <c r="U21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="2:26">
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="V22" s="4"/>
+      <c r="V22" s="6"/>
     </row>
     <row r="23" spans="2:26">
-      <c r="B23" s="3"/>
+      <c r="B23" s="5"/>
     </row>
     <row r="30" spans="2:26">
       <c r="B30"/>
     </row>
     <row r="32" spans="2:26">
-      <c r="C32" s="9"/>
+      <c r="C32" s="10"/>
     </row>
     <row r="33" spans="29:29">
-      <c r="AC33" s="4"/>
+      <c r="AC33" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4842,7 +4843,7 @@
       <c r="R6" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="S6" s="7"/>
+      <c r="S6" s="2"/>
     </row>
     <row r="7" spans="2:19">
       <c r="C7" s="1" t="s">
@@ -5014,13 +5015,13 @@
       <c r="B11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="5"/>
     </row>
     <row r="12" spans="2:23">
-      <c r="V12" s="4"/>
+      <c r="V12" s="6"/>
     </row>
     <row r="13" spans="2:23">
-      <c r="C13" s="3"/>
+      <c r="C13" s="5"/>
     </row>
     <row r="14" spans="2:23">
       <c r="B14" s="1" t="s">
@@ -5034,11 +5035,11 @@
       <c r="B15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="7"/>
     </row>
     <row r="16" spans="2:23">
-      <c r="C16" s="6"/>
-      <c r="V16" s="4"/>
+      <c r="C16" s="8"/>
+      <c r="V16" s="6"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -5067,7 +5068,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="4"/>
+      <c r="AC23" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -5109,7 +5110,7 @@
       <c r="B6" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="S6" s="4" t="s">
         <v>211</v>
       </c>
     </row>
@@ -5249,7 +5250,7 @@
       <c r="A6" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="S6" s="2"/>
+      <c r="S6" s="4"/>
     </row>
     <row r="7" spans="1:24">
       <c r="B7" s="1" t="s">
@@ -5361,6 +5362,150 @@
       </c>
       <c r="X31" s="1" t="s">
         <v>484</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:V27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:22">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="2:22">
+      <c r="C2" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22">
+      <c r="C3" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22">
+      <c r="C5" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="2:22">
+      <c r="C6" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="S6" s="2"/>
+    </row>
+    <row r="8" spans="2:22">
+      <c r="C8" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22">
+      <c r="C9" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22">
+      <c r="C11" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="C12" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22">
+      <c r="C14" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22">
+      <c r="C15" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="17" spans="3:22">
+      <c r="C17" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22">
+      <c r="C18" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="20" spans="3:22">
+      <c r="C20" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22">
+      <c r="C21" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22">
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="3:22">
+      <c r="C23" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22">
+      <c r="C24" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22">
+      <c r="C26" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22">
+      <c r="C27" s="1" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -5442,7 +5587,7 @@
       <c r="B11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="5"/>
       <c r="P11" s="1" t="s">
         <v>68</v>
       </c>
@@ -5451,13 +5596,13 @@
       <c r="C12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V12" s="4"/>
+      <c r="V12" s="6"/>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="5"/>
       <c r="P13" s="1" t="s">
         <v>71</v>
       </c>
@@ -5471,16 +5616,16 @@
       <c r="B15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="7"/>
       <c r="P15" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="6"/>
     </row>
     <row r="17" spans="2:29">
       <c r="B17" s="1" t="s">
@@ -5528,7 +5673,7 @@
       <c r="P23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AC23" s="4"/>
+      <c r="AC23" s="6"/>
     </row>
     <row r="24" spans="2:29">
       <c r="C24" s="1" t="s">
@@ -5622,13 +5767,13 @@
       <c r="B11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="5"/>
     </row>
     <row r="12" spans="2:23">
-      <c r="V12" s="4"/>
+      <c r="V12" s="6"/>
     </row>
     <row r="13" spans="2:23">
-      <c r="C13" s="3"/>
+      <c r="C13" s="5"/>
     </row>
     <row r="14" spans="2:23">
       <c r="B14" s="1" t="s">
@@ -5642,11 +5787,11 @@
       <c r="B15" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="7"/>
     </row>
     <row r="16" spans="2:23">
-      <c r="C16" s="6"/>
-      <c r="V16" s="4"/>
+      <c r="C16" s="8"/>
+      <c r="V16" s="6"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -5675,7 +5820,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="4"/>
+      <c r="AC23" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -5740,16 +5885,16 @@
       </c>
     </row>
     <row r="11" spans="2:26">
-      <c r="C11" s="3"/>
+      <c r="C11" s="5"/>
     </row>
     <row r="12" spans="2:26">
       <c r="B12" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="V12" s="4"/>
+      <c r="V12" s="6"/>
     </row>
     <row r="13" spans="2:26">
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>122</v>
       </c>
     </row>
@@ -5762,16 +5907,16 @@
       <c r="B15" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="7"/>
       <c r="Z15" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="16" spans="2:26">
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="6"/>
     </row>
     <row r="17" spans="2:29">
       <c r="Z17" s="1" t="s">
@@ -5810,7 +5955,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="4"/>
+      <c r="AC23" s="6"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">
@@ -5888,7 +6033,7 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="3"/>
+      <c r="C11" s="5"/>
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="1" t="s">
@@ -5899,7 +6044,7 @@
       </c>
     </row>
     <row r="13" spans="2:22">
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5907,16 +6052,16 @@
       <c r="B15" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="7"/>
       <c r="V15" s="1" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="V16" s="4"/>
+      <c r="V16" s="6"/>
     </row>
     <row r="18" spans="2:29">
       <c r="B18" s="1" t="s">
@@ -5945,7 +6090,7 @@
       </c>
     </row>
     <row r="23" spans="2:29">
-      <c r="AC23" s="4"/>
+      <c r="AC23" s="6"/>
     </row>
     <row r="24" spans="2:29">
       <c r="B24" s="1" t="s">
@@ -6242,7 +6387,7 @@
       <c r="B6" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="S6" s="7" t="s">
+      <c r="S6" s="2" t="s">
         <v>211</v>
       </c>
     </row>

--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="13" activeTab="23"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="14" activeTab="24"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -36,6 +36,7 @@
     <sheet name="20260830" sheetId="96" r:id="rId22"/>
     <sheet name="20260906" sheetId="97" r:id="rId23"/>
     <sheet name="20260913" sheetId="98" r:id="rId24"/>
+    <sheet name="20260927" sheetId="99" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="515">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -1665,6 +1666,96 @@
   </si>
   <si>
     <t>B: I’ve got it. You must never do exercise on an empty stomach.</t>
+  </si>
+  <si>
+    <t>A：中秋快到了，你怎么过？</t>
+  </si>
+  <si>
+    <t>A: Mid-Autumn is coming, how will you spend it?</t>
+  </si>
+  <si>
+    <t>A: Zhōng qiū kuài dào le, nǐ zěn me guò?</t>
+  </si>
+  <si>
+    <t>B：和爸妈吃团圆饭，晚上赏月。</t>
+  </si>
+  <si>
+    <t>B: Have a family dinner with parents, admire the moon at night.</t>
+  </si>
+  <si>
+    <t>B: Hé bàmā chī tuányuánfàn, wǎnshàng shǎngyuè.</t>
+  </si>
+  <si>
+    <t>A：家里会做特色菜吗？</t>
+  </si>
+  <si>
+    <t>A: Will your family cook special dishes?</t>
+  </si>
+  <si>
+    <t>A: Jiālǐ huì zuò tèsècài ma?</t>
+  </si>
+  <si>
+    <t>B：会的，还准备了月饼。</t>
+  </si>
+  <si>
+    <t>B: Yes, mooncakes are also prepared.</t>
+  </si>
+  <si>
+    <t>B: Huì de, hái zhǔnbèi le yuèbǐng.</t>
+  </si>
+  <si>
+    <t>A：我家每年都在阳台等月亮升起。</t>
+  </si>
+  <si>
+    <t>A: My family waits for the moon on the balcony every year.</t>
+  </si>
+  <si>
+    <t>A: Wǒjiā měinián dōu zài yángtái děng yuèliàng shēngqǐ.</t>
+  </si>
+  <si>
+    <t>B：奶奶说中秋月亮是全年最亮的。</t>
+  </si>
+  <si>
+    <t>B: Grandma says Mid-Autumn moon is the brightest of the year.</t>
+  </si>
+  <si>
+    <t>B: Nǎinai shuō zhōngqiū yuèliàng shì quánnián zuìliàng de.</t>
+  </si>
+  <si>
+    <t>A：对，古人说月是故乡明。</t>
+  </si>
+  <si>
+    <t>A: Right, old saying goes "moon is brightest at hometown".</t>
+  </si>
+  <si>
+    <t>A: Duì, gǔrén shuō yuè shì gùxiāngmíng.</t>
+  </si>
+  <si>
+    <t>B：今晚来我家一起赏月吧？</t>
+  </si>
+  <si>
+    <t>B: Come to my home for moon-watching tonight?</t>
+  </si>
+  <si>
+    <t>B: Jīnwǎn lái wǒjiā yīqǐ shǎngyuè ba?</t>
+  </si>
+  <si>
+    <t>A：好，我带些中秋点心过去。</t>
+  </si>
+  <si>
+    <t>A: Sure, I'll bring some Mid-Autumn snacks.</t>
+  </si>
+  <si>
+    <t>A: Hǎo, wǒ dài xiē zhōngqiū diǎnxīn guòqù.</t>
+  </si>
+  <si>
+    <t>B：说定了，傍晚我在路口等你。</t>
+  </si>
+  <si>
+    <t>B: It's a deal, I'll wait for you at the corner at dusk.</t>
+  </si>
+  <si>
+    <t>B: Shuōdìng le, bàngwǎn wǒ zài lùkǒu děng nǐ.</t>
   </si>
 </sst>
 </file>
@@ -5515,6 +5606,160 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:X31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:24">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:24">
+      <c r="B3" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="4" spans="2:24">
+      <c r="C4" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="2:24">
+      <c r="B6" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="S6" s="2"/>
+      <c r="X6" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24">
+      <c r="C7" s="1" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24">
+      <c r="B9" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24">
+      <c r="C10" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24">
+      <c r="B12" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="13" spans="2:24">
+      <c r="C13" s="1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="15" spans="2:24">
+      <c r="B15" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="16" spans="2:24">
+      <c r="C16" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="18" spans="2:24">
+      <c r="B18" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="19" spans="2:24">
+      <c r="C19" s="1" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="21" spans="2:24">
+      <c r="B21" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="22" spans="2:24">
+      <c r="C22" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="24" spans="2:24">
+      <c r="B24" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="25" spans="2:24">
+      <c r="C25" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="27" spans="2:24">
+      <c r="B27" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="28" spans="2:24">
+      <c r="C28" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="30" spans="2:24">
+      <c r="B30" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="X30" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="31" spans="2:24">
+      <c r="C31" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>

--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="14" activeTab="24"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="15" activeTab="25"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -37,6 +37,7 @@
     <sheet name="20260906" sheetId="97" r:id="rId23"/>
     <sheet name="20260913" sheetId="98" r:id="rId24"/>
     <sheet name="20260927" sheetId="99" r:id="rId25"/>
+    <sheet name="20261004" sheetId="100" r:id="rId26"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="524">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -1756,6 +1757,33 @@
   </si>
   <si>
     <t>B: Shuōdìng le, bàngwǎn wǒ zài lùkǒu děng nǐ.</t>
+  </si>
+  <si>
+    <t>A: 外面正在下大雨呢！我今天早上没看天气预报。</t>
+  </si>
+  <si>
+    <t>Wàimiàn zhèngzài xiadàyǔ ne! Wǒ jīntiān zǎoshàng méikàn tiānqì yùbào.</t>
+  </si>
+  <si>
+    <t>Wǒ yě méikàn! Wǒ běnlái dǎsuàn wǔfànhòu qù túshūguǎn xuéxí de</t>
+  </si>
+  <si>
+    <t>Nǐ yǒu duōyú de yǔsǎn jiè gěi wǒ ma? Wǒ děi huísùshè qǔ bǐjìběn.</t>
+  </si>
+  <si>
+    <t>dāngrán yǒu a! Wǒ de bāolǐ zǒngshì fàngzhe yī bǎ zhédiésǎn, jiù shì wèile yǔtiān zhǔnbèi de.</t>
+  </si>
+  <si>
+    <t>zhēn shì gè hǎoxíguàn. Jīntiān xiàwǔ zhè cháng yǔ xiàde tài tūrán le.</t>
+  </si>
+  <si>
+    <t>qíshí wǒ hěnxǐhuan yǔ hòu de wèidào,  hen qīngxīn , tèbié shūfu.</t>
+  </si>
+  <si>
+    <t>A: 是啊，我也这么觉得！但是在大雨里走路总是把鞋弄湿。</t>
+  </si>
+  <si>
+    <t>shì a, wǒ yě zhè me juéde! dànshì zài dàyǔ lǐ zǒulù zǒngshì bǎ xié nòngshī.</t>
   </si>
 </sst>
 </file>
@@ -5760,6 +5788,138 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:V25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:22">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22">
+      <c r="B3" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22">
+      <c r="C4" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="2:22">
+      <c r="B6" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="S6" s="2"/>
+      <c r="V6" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22">
+      <c r="C7" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22">
+      <c r="B9" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22">
+      <c r="C10" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="B12" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22">
+      <c r="V13" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22">
+      <c r="C14" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22">
+      <c r="B15" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22">
+      <c r="C16" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22">
+      <c r="B18" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22">
+      <c r="C19" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22">
+      <c r="B21" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22">
+      <c r="V22" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22">
+      <c r="C23" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="B24" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="C25" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>

--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="15" activeTab="25"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="16" activeTab="26"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -38,6 +38,7 @@
     <sheet name="20260913" sheetId="98" r:id="rId24"/>
     <sheet name="20260927" sheetId="99" r:id="rId25"/>
     <sheet name="20261004" sheetId="100" r:id="rId26"/>
+    <sheet name="20261011" sheetId="101" r:id="rId27"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="525">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -1784,6 +1785,9 @@
   </si>
   <si>
     <t>shì a, wǒ yě zhè me juéde! dànshì zài dàyǔ lǐ zǒulù zǒngshì bǎ xié nòngshī.</t>
+  </si>
+  <si>
+    <t>Shì de, wàn yī lúntāi lòuqì ne.</t>
   </si>
 </sst>
 </file>
@@ -5920,6 +5924,133 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:T23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:20">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:20">
+      <c r="B3" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20">
+      <c r="C4" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20">
+      <c r="B5" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20">
+      <c r="C6" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20">
+      <c r="B7" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20">
+      <c r="C8" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20">
+      <c r="B10" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20">
+      <c r="C11" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20">
+      <c r="B13" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20">
+      <c r="C14" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20">
+      <c r="B16" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20">
+      <c r="C17" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="2:20">
+      <c r="B19" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="2:20">
+      <c r="C20" s="1" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20">
+      <c r="B22" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20">
+      <c r="C23" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>

--- a/learn_chinese2026.xlsx
+++ b/learn_chinese2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="16" activeTab="26"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="751" firstSheet="17" activeTab="27"/>
   </bookViews>
   <sheets>
     <sheet name="20260208" sheetId="73" r:id="rId1"/>
@@ -39,6 +39,7 @@
     <sheet name="20260927" sheetId="99" r:id="rId25"/>
     <sheet name="20261004" sheetId="100" r:id="rId26"/>
     <sheet name="20261011" sheetId="101" r:id="rId27"/>
+    <sheet name="20261018" sheetId="102" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="556">
   <si>
     <t>Chinese Lessons：</t>
   </si>
@@ -1788,6 +1789,99 @@
   </si>
   <si>
     <t>Shì de, wàn yī lúntāi lòuqì ne.</t>
+  </si>
+  <si>
+    <t>Autumn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A: 天气凉快了，秋天来了。 </t>
+  </si>
+  <si>
+    <t>A: The weather is cool. Autumn is coming.</t>
+  </si>
+  <si>
+    <t>tiānqì liángkuai le, qiūtiān lái le.</t>
+  </si>
+  <si>
+    <t>B: 是啊，我最喜欢秋天。</t>
+  </si>
+  <si>
+    <t>B: Yes, I like autumn best.</t>
+  </si>
+  <si>
+    <t>shì a, wǒ zuì xǐhuan qiūtiān.</t>
+  </si>
+  <si>
+    <t>A: 你看，树叶变黄了。</t>
+  </si>
+  <si>
+    <t>A: Look, the leaves turn yellow.</t>
+  </si>
+  <si>
+    <t>nǐ kàn, shùyè biàn huáng le.</t>
+  </si>
+  <si>
+    <t>B: 多美啊！还有红叶。</t>
+  </si>
+  <si>
+    <t>B: How beautiful! There are also red leaves.</t>
+  </si>
+  <si>
+    <t>duō měi a! hái yǒu hóngyè.</t>
+  </si>
+  <si>
+    <t>A: 秋天的果子都熟了。</t>
+  </si>
+  <si>
+    <t>A: 1. Fruits are ripe in autumn.</t>
+  </si>
+  <si>
+    <t>qiūtiān de guǒzi dōu shú le.</t>
+  </si>
+  <si>
+    <t>B: 我喜欢吃苹果和橘子。</t>
+  </si>
+  <si>
+    <t>B: I like eating apples and oranges.</t>
+  </si>
+  <si>
+    <t>wǒ xǐhuan chī píngguǒ hé júzi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A:我们下午去公园散步吧。 </t>
+  </si>
+  <si>
+    <t>A: Let’s go for a walk in the park this afternoon.</t>
+  </si>
+  <si>
+    <t>wǒmen xiàwǔ qù gōngyuán sànbù ba.</t>
+  </si>
+  <si>
+    <t>B:好啊！可以拍照。</t>
+  </si>
+  <si>
+    <t>B:  Great! We can take photos.</t>
+  </si>
+  <si>
+    <t>hǎo a! kěyǐ pāi zhào</t>
+  </si>
+  <si>
+    <t>A:记得穿厚衣服，别感冒。</t>
+  </si>
+  <si>
+    <t>A:Remember to wear thick clothes. Don’t catch a cold</t>
+  </si>
+  <si>
+    <t>jìde chuān hòu yīfu, bié gǎnmào.</t>
+  </si>
+  <si>
+    <t>B: 好的，我会小心的。</t>
+  </si>
+  <si>
+    <t>B:OK. I will be careful.</t>
+  </si>
+  <si>
+    <t>hǎo de, wǒ huì xiǎoxīn de.</t>
   </si>
 </sst>
 </file>
@@ -6051,6 +6145,164 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:P23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="7" width="2.63888888888889" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.73148148148148" style="1" customWidth="1"/>
+    <col min="9" max="1024" width="2.63888888888889" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:16">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16">
+      <c r="C2" s="1" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16">
+      <c r="B3" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16">
+      <c r="C4" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16">
+      <c r="B5" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16">
+      <c r="C6" s="1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16">
+      <c r="B7" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16">
+      <c r="C8" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16">
+      <c r="B9" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16">
+      <c r="C10" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16">
+      <c r="B11" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16">
+      <c r="C12" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16">
+      <c r="B14" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16">
+      <c r="C15" s="1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16">
+      <c r="B16" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16">
+      <c r="C17" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16">
+      <c r="B18" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16">
+      <c r="C19" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16">
+      <c r="B20" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16">
+      <c r="C21" s="1" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16">
+      <c r="B22" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16">
+      <c r="C23" s="1" t="s">
+        <v>555</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
